--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0F21A1-8F42-4F27-A4DF-777068313FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36E7871-E17A-4BA0-B2CD-F47F614DACA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="1755" windowWidth="27435" windowHeight="14940" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="855" yWindow="540" windowWidth="27435" windowHeight="14940" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>26</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36E7871-E17A-4BA0-B2CD-F47F614DACA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A9CD46-A185-4D7D-AB80-C6596E73796B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="540" windowWidth="27435" windowHeight="14940" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="1935" yWindow="75" windowWidth="27780" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -96,176 +96,172 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Emsv_R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Emsv_B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Emsv_G</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_Body_diffuse.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_Body_specular.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_head_diffuse.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_head_specular.png</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/rust_coarse_01_arm_1k.jpg</t>
+  </si>
+  <si>
+    <t>AssultRifle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Soldier_body</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Soldier_head</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Light_Img.png</t>
+  </si>
+  <si>
+    <t>DirLight</t>
+  </si>
+  <si>
+    <t>Canonn</t>
+  </si>
+  <si>
+    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant_n.png</t>
+  </si>
+  <si>
+    <t>Ant</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B_2</t>
+  </si>
+  <si>
+    <t>Resource/Model/b-2/textures/ggg_diffuseOriginal.jpeg</t>
+  </si>
+  <si>
+    <t>Resource/Model/b-2/textures/ggg_metallic.jpeg</t>
+  </si>
+  <si>
+    <t>Resource/Model/Claymore/Mat_Base_Color.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Claymore/Mat_Roughness.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Claymore/Mat_Normal_DirectX.png</t>
+  </si>
+  <si>
+    <t>Claymore</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>Resource/Model/Building/01/texture/building5-lo.jpg</t>
+  </si>
+  <si>
     <t>Resource/Texture/DefaultN_Map.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Emsv_R</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Emsv_B</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Emsv_G</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_Body_diffuse.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_Body_specular.png</t>
+  </si>
+  <si>
+    <t>MotherShip</t>
+  </si>
+  <si>
+    <t>Resource/Texture/metal_plate_02_diff_2k.jpg</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>Resource/Texture/aerial_grass_rock_nor_dx_4k.png</t>
+  </si>
+  <si>
+    <t>Billboard</t>
+  </si>
+  <si>
+    <t>PointLight</t>
+  </si>
+  <si>
+    <t>PlayerModel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_W040.jpg</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_W040_n.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_S050.jpg</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_W030.jpg</t>
+  </si>
+  <si>
+    <t>Decal_BulletHole</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Decal_Ant_Splash</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/aerial_grass_rock_diff_4k.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Billboard.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/BulletHole.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Acid.png</t>
   </si>
   <si>
     <t>Resource/Model/Player/textures/Soldier_Body_normal.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_head_diffuse.png</t>
   </si>
   <si>
     <t>Resource/Model/Player/textures/Soldier_head_normal.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_head_specular.png</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/rust_coarse_01_arm_1k.jpg</t>
-  </si>
-  <si>
-    <t>AssultRifle</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Soldier_body</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Soldier_head</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Light_Img.png</t>
-  </si>
-  <si>
-    <t>DirLight</t>
-  </si>
-  <si>
-    <t>Canonn</t>
-  </si>
-  <si>
-    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant_n.png</t>
-  </si>
-  <si>
-    <t>Ant</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>B_2</t>
-  </si>
-  <si>
-    <t>Resource/Model/b-2/textures/ggg_diffuseOriginal.jpeg</t>
-  </si>
-  <si>
-    <t>Resource/Model/b-2/textures/ggg_metallic.jpeg</t>
-  </si>
-  <si>
-    <t>Resource/Model/Claymore/Mat_Base_Color.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Claymore/Mat_Roughness.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Claymore/Mat_Normal_DirectX.png</t>
-  </si>
-  <si>
-    <t>Claymore</t>
-  </si>
-  <si>
-    <t>Building</t>
-  </si>
-  <si>
-    <t>Resource/Model/Building/01/texture/building5-lo.jpg</t>
-  </si>
-  <si>
-    <t>Resource/Texture/DefaultN_Map.png</t>
-  </si>
-  <si>
-    <t>MotherShip</t>
-  </si>
-  <si>
-    <t>Resource/Texture/metal_plate_02_diff_2k.jpg</t>
-  </si>
-  <si>
-    <t>Ground</t>
-  </si>
-  <si>
-    <t>Resource/Texture/aerial_grass_rock_nor_dx_4k.png</t>
-  </si>
-  <si>
-    <t>Resource/Texture/0191.png</t>
-  </si>
-  <si>
-    <t>Billboard</t>
-  </si>
-  <si>
-    <t>PointLight</t>
   </si>
   <si>
     <t>Resource/Model/b-2/textures/ggg_normal.jpeg</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PlayerModel</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Wall_W040.jpg</t>
-  </si>
-  <si>
-    <t>Resource/Texture/Wall_W040_n.png</t>
-  </si>
-  <si>
-    <t>Resource/Texture/Wall_S050.jpg</t>
-  </si>
-  <si>
-    <t>Resource/Texture/Wall_W030.jpg</t>
-  </si>
-  <si>
-    <t>Resource/Texture/water_surface02.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Decal_BulletHole</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/BulletHole.png</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Resource/Texture/BulletHole_n.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Decal_Ant_Splash</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Resource/Texture/Acid_n.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Acid.png</t>
+  </si>
+  <si>
+    <t>RocketLauncher</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Weapon/RocketLauncher/Simple rocket launcher Tex.png</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -304,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -369,19 +365,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -424,6 +407,78 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -432,7 +487,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -457,7 +512,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -794,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -809,43 +882,43 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="14" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -863,7 +936,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2">
         <v>0.4</v>
@@ -886,13 +959,13 @@
       <c r="H2" s="2">
         <v>1</v>
       </c>
-      <c r="I2" s="2">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3">
         <v>150</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="11">
         <v>0</v>
       </c>
       <c r="L2" s="2">
@@ -901,16 +974,16 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="N2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="8">
         <v>-1</v>
       </c>
       <c r="R2" s="2">
@@ -919,7 +992,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
@@ -942,13 +1015,13 @@
       <c r="H3" s="3">
         <v>1</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="10">
         <v>1</v>
       </c>
       <c r="J3" s="3">
         <v>50</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="12">
         <v>0</v>
       </c>
       <c r="L3" s="3">
@@ -960,14 +1033,14 @@
       <c r="N3" s="3">
         <v>0</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -975,7 +1048,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -998,13 +1071,13 @@
       <c r="H4" s="3">
         <v>1</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="10">
         <v>1</v>
       </c>
       <c r="J4" s="3">
         <v>50</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="12">
         <v>0</v>
       </c>
       <c r="L4" s="3">
@@ -1016,14 +1089,14 @@
       <c r="N4" s="3">
         <v>0</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>24</v>
+      <c r="O4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -1031,7 +1104,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1054,13 +1127,13 @@
       <c r="H5" s="3">
         <v>1</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="10">
         <v>1</v>
       </c>
       <c r="J5" s="3">
         <v>200</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="12">
         <v>0</v>
       </c>
       <c r="L5" s="3">
@@ -1072,13 +1145,13 @@
       <c r="N5" s="3">
         <v>25</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="2">
+      <c r="O5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="8">
         <v>-1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="8">
         <v>-1</v>
       </c>
       <c r="R5" s="2">
@@ -1087,7 +1160,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1110,13 +1183,13 @@
       <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="10">
         <v>1</v>
       </c>
       <c r="J6" s="3">
         <v>100</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="12">
         <v>0</v>
       </c>
       <c r="L6" s="3">
@@ -1128,13 +1201,13 @@
       <c r="N6" s="3">
         <v>0</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P6" s="2">
+      <c r="O6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" s="8">
         <v>-1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="8">
         <v>-1</v>
       </c>
       <c r="R6" s="2">
@@ -1143,7 +1216,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1166,13 +1239,13 @@
       <c r="H7" s="3">
         <v>1</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="10">
         <v>1</v>
       </c>
       <c r="J7" s="3">
         <v>100</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="12">
         <v>1</v>
       </c>
       <c r="L7" s="3">
@@ -1184,13 +1257,13 @@
       <c r="N7" s="3">
         <v>0.1</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="O7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="8">
         <v>-1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="8">
         <v>-1</v>
       </c>
       <c r="R7" s="2">
@@ -1199,7 +1272,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -1222,13 +1295,13 @@
       <c r="H8" s="3">
         <v>1</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="3">
         <v>20</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="12">
         <v>0</v>
       </c>
       <c r="L8" s="3">
@@ -1240,13 +1313,13 @@
       <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q8" s="2">
+      <c r="O8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q8" s="8">
         <v>-1</v>
       </c>
       <c r="R8" s="2">
@@ -1255,7 +1328,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -1278,13 +1351,13 @@
       <c r="H9" s="3">
         <v>0.5</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="10">
         <v>1</v>
       </c>
       <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="12">
         <v>0</v>
       </c>
       <c r="L9" s="3">
@@ -1296,13 +1369,13 @@
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q9" s="2">
+      <c r="O9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="8">
         <v>-1</v>
       </c>
       <c r="R9" s="2">
@@ -1311,7 +1384,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -1334,13 +1407,13 @@
       <c r="H10" s="3">
         <v>1</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="10">
         <v>1</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="12">
         <v>0</v>
       </c>
       <c r="L10" s="3">
@@ -1352,14 +1425,14 @@
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>38</v>
+      <c r="O10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="R10" s="2">
         <v>0</v>
@@ -1367,7 +1440,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -1390,13 +1463,13 @@
       <c r="H11" s="3">
         <v>1</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="10">
         <v>1</v>
       </c>
       <c r="J11" s="3">
         <v>200</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="12">
         <v>0</v>
       </c>
       <c r="L11" s="3">
@@ -1408,14 +1481,14 @@
       <c r="N11" s="3">
         <v>0</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>40</v>
+      <c r="O11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
@@ -1423,7 +1496,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1446,13 +1519,13 @@
       <c r="H12" s="3">
         <v>1</v>
       </c>
-      <c r="I12" s="3">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="I12" s="10">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
         <v>150</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="12">
         <v>0</v>
       </c>
       <c r="L12" s="3">
@@ -1464,13 +1537,13 @@
       <c r="N12" s="3">
         <v>0</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q12" s="2">
+      <c r="O12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="8">
         <v>-1</v>
       </c>
       <c r="R12" s="2">
@@ -1479,7 +1552,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1502,13 +1575,13 @@
       <c r="H13" s="3">
         <v>1</v>
       </c>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
+      <c r="I13" s="10">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
         <v>150</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="12">
         <v>0</v>
       </c>
       <c r="L13" s="3">
@@ -1520,13 +1593,13 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13" s="2">
+      <c r="O13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" s="8">
         <v>-1</v>
       </c>
       <c r="R13" s="2">
@@ -1535,7 +1608,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1558,13 +1631,13 @@
       <c r="H14" s="3">
         <v>1</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="10">
         <v>1</v>
       </c>
       <c r="J14" s="3">
-        <v>100</v>
-      </c>
-      <c r="K14" s="3">
+        <v>50</v>
+      </c>
+      <c r="K14" s="12">
         <v>1</v>
       </c>
       <c r="L14" s="3">
@@ -1574,15 +1647,15 @@
         <v>1</v>
       </c>
       <c r="N14" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q14" s="8">
         <v>-1</v>
       </c>
       <c r="R14" s="2">
@@ -1591,7 +1664,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1614,13 +1687,13 @@
       <c r="H15" s="3">
         <v>1</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="3">
         <v>50</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="12">
         <v>0</v>
       </c>
       <c r="L15" s="3">
@@ -1632,13 +1705,13 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P15" s="2">
+      <c r="O15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="P15" s="8">
         <v>-1</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="8">
         <v>-1</v>
       </c>
       <c r="R15" s="2">
@@ -1647,7 +1720,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -1670,13 +1743,13 @@
       <c r="H16" s="3">
         <v>1</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="10">
         <v>1</v>
       </c>
       <c r="J16" s="3">
         <v>50</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="12">
         <v>1</v>
       </c>
       <c r="L16" s="3">
@@ -1688,13 +1761,13 @@
       <c r="N16" s="3">
         <v>0.1</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q16" s="2">
+      <c r="O16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q16" s="8">
         <v>-1</v>
       </c>
       <c r="R16" s="2">
@@ -1703,7 +1776,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
@@ -1726,13 +1799,13 @@
       <c r="H17" s="3">
         <v>1</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="10">
         <v>1</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="12">
         <v>1</v>
       </c>
       <c r="L17" s="3">
@@ -1744,13 +1817,13 @@
       <c r="N17" s="3">
         <v>1</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="O17" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q17" s="8">
         <v>-1</v>
       </c>
       <c r="R17" s="3">
@@ -1759,7 +1832,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -1782,13 +1855,13 @@
       <c r="H18" s="3">
         <v>1</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="10">
         <v>1</v>
       </c>
       <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="12">
         <v>1</v>
       </c>
       <c r="L18" s="3">
@@ -1798,18 +1871,74 @@
         <v>1</v>
       </c>
       <c r="N18" s="3">
-        <v>1</v>
-      </c>
-      <c r="O18" s="3" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="10">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3">
+        <v>100</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="P19" s="8">
         <v>-1</v>
       </c>
-      <c r="R18" s="3">
+      <c r="Q19" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R19" s="2">
         <v>0</v>
       </c>
     </row>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A9CD46-A185-4D7D-AB80-C6596E73796B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBED311-EE57-438B-AFC3-FD0F3F2A141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="75" windowWidth="27780" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="240" yWindow="1365" windowWidth="27780" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -108,18 +108,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Resource/Model/Player/textures/Soldier_Body_diffuse.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_Body_specular.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_head_diffuse.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_head_specular.png</t>
-  </si>
-  <si>
     <t>Bullet</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -242,12 +230,6 @@
     <t>Resource/Texture/Acid.png</t>
   </si>
   <si>
-    <t>Resource/Model/Player/textures/Soldier_Body_normal.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Player/textures/Soldier_head_normal.png</t>
-  </si>
-  <si>
     <t>Resource/Model/b-2/textures/ggg_normal.jpeg</t>
   </si>
   <si>
@@ -262,6 +244,30 @@
   </si>
   <si>
     <t>Resource/Model/Weapon/RocketLauncher/Simple rocket launcher Tex.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Ranger/Textures/Soldier_Body_diffuse.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Ranger/Textures/Soldier_Body_normal.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Ranger/Textures/Soldier_Body_specular.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Ranger/Textures/Soldier_head_diffuse.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Ranger/Textures/Soldier_head_normal.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Ranger/Textures/Soldier_head_specular.png</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -936,7 +942,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2">
         <v>0.4</v>
@@ -978,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="8">
         <v>-1</v>
@@ -992,7 +998,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
@@ -1034,13 +1040,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -1048,7 +1054,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1090,13 +1096,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -1104,7 +1110,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1146,7 +1152,7 @@
         <v>25</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P5" s="8">
         <v>-1</v>
@@ -1160,7 +1166,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1202,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="P6" s="8">
         <v>-1</v>
@@ -1216,7 +1222,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1258,7 +1264,7 @@
         <v>0.1</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P7" s="8">
         <v>-1</v>
@@ -1272,7 +1278,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -1314,10 +1320,10 @@
         <v>200</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q8" s="8">
         <v>-1</v>
@@ -1328,7 +1334,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -1370,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q9" s="8">
         <v>-1</v>
@@ -1384,7 +1390,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -1426,13 +1432,13 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R10" s="2">
         <v>0</v>
@@ -1440,7 +1446,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -1482,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
@@ -1496,7 +1502,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1538,10 +1544,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q12" s="8">
         <v>-1</v>
@@ -1552,7 +1558,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1594,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q13" s="8">
         <v>-1</v>
@@ -1608,7 +1614,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1650,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="8">
         <v>-1</v>
@@ -1664,7 +1670,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1706,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P15" s="8">
         <v>-1</v>
@@ -1720,7 +1726,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -1762,10 +1768,10 @@
         <v>0.1</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q16" s="8">
         <v>-1</v>
@@ -1776,7 +1782,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
@@ -1818,10 +1824,10 @@
         <v>1</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Q17" s="8">
         <v>-1</v>
@@ -1832,7 +1838,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -1874,10 +1880,10 @@
         <v>1.5</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q18" s="8">
         <v>-1</v>
@@ -1888,7 +1894,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
@@ -1930,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="P19" s="8">
         <v>-1</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBED311-EE57-438B-AFC3-FD0F3F2A141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382F9A38-A924-462C-A9FF-2FD9EA2E0A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="1365" windowWidth="27780" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="1170" yWindow="1125" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="76">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -268,6 +268,42 @@
   </si>
   <si>
     <t>Resource/Model/Ranger/Textures/Soldier_head_specular.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Building01_Top</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Building/02/Textures/tex01.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Building01_Base1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Building01_Base2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Building01_Base3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/DefaultN_Map.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Building/02/Textures/tex04.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Building/02/Textures/tex02.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Building/02/Textures/tex03.jpg</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -873,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1502,7 +1538,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1544,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="8">
         <v>-1</v>
@@ -1558,7 +1594,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1600,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>38</v>
@@ -1614,7 +1650,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1641,25 +1677,25 @@
         <v>1</v>
       </c>
       <c r="J14" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q14" s="8">
         <v>-1</v>
@@ -1670,7 +1706,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1697,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K15" s="12">
         <v>0</v>
@@ -1712,21 +1748,21 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="P15" s="8">
-        <v>-1</v>
+        <v>75</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="Q15" s="8">
         <v>-1</v>
       </c>
       <c r="R15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -1753,25 +1789,25 @@
         <v>1</v>
       </c>
       <c r="J16" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K16" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q16" s="8">
         <v>-1</v>
@@ -1782,7 +1818,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
@@ -1809,36 +1845,36 @@
         <v>1</v>
       </c>
       <c r="J17" s="3">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K17" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="Q17" s="8">
         <v>-1</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -1865,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K18" s="12">
         <v>1</v>
@@ -1877,24 +1913,24 @@
         <v>1</v>
       </c>
       <c r="N18" s="3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="Q18" s="8">
         <v>-1</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
@@ -1921,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K19" s="12">
         <v>0</v>
@@ -1936,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P19" s="8">
         <v>-1</v>
@@ -1945,6 +1981,230 @@
         <v>-1</v>
       </c>
       <c r="R19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="10">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3">
+        <v>50</v>
+      </c>
+      <c r="K20" s="12">
+        <v>1</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="10">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3">
+        <v>100</v>
+      </c>
+      <c r="K21" s="12">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="10">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
+        <v>100</v>
+      </c>
+      <c r="K22" s="12">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3">
+        <v>100</v>
+      </c>
+      <c r="K23" s="12">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="P23" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R23" s="2">
         <v>0</v>
       </c>
     </row>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382F9A38-A924-462C-A9FF-2FD9EA2E0A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821EB397-3209-4436-AF4E-B76329AB3D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1125" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="165" yWindow="360" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="78">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -305,6 +305,12 @@
   <si>
     <t>Resource/Model/Building/02/Textures/tex03.jpg</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LaserPointBillboard</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/Particle04_bokashi_hard.png</t>
   </si>
 </sst>
 </file>
@@ -342,7 +348,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -523,13 +529,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -574,6 +626,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -909,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1929,46 +1996,46 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="3">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1</v>
-      </c>
-      <c r="I19" s="10">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3">
+      <c r="B19" s="15">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15">
+        <v>1</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
+        <v>1</v>
+      </c>
+      <c r="F19" s="15">
+        <v>1</v>
+      </c>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15">
+        <v>1</v>
+      </c>
+      <c r="I19" s="16">
+        <v>1</v>
+      </c>
+      <c r="J19" s="15">
         <v>50</v>
       </c>
-      <c r="K19" s="12">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
+      <c r="K19" s="17">
+        <v>0</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15">
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
@@ -1980,13 +2047,13 @@
       <c r="Q19" s="8">
         <v>-1</v>
       </c>
-      <c r="R19" s="2">
+      <c r="R19" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A20" s="3" t="s">
-        <v>44</v>
+      <c r="A20" s="19" t="s">
+        <v>76</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2009,96 +2076,96 @@
       <c r="H20" s="3">
         <v>1</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="3">
         <v>1</v>
       </c>
       <c r="J20" s="3">
         <v>50</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="3">
         <v>1</v>
       </c>
       <c r="L20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>-1</v>
-      </c>
-      <c r="R20" s="2">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="O20" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-1</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-1</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="9">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
         <v>50</v>
       </c>
-      <c r="B21" s="3">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1</v>
-      </c>
-      <c r="I21" s="10">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3">
-        <v>100</v>
-      </c>
-      <c r="K21" s="12">
-        <v>1</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1</v>
-      </c>
-      <c r="M21" s="3">
-        <v>1</v>
-      </c>
-      <c r="N21" s="3">
-        <v>1</v>
+      <c r="K21" s="11">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0.1</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="Q21" s="8">
         <v>-1</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2137,13 +2204,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q22" s="8">
         <v>-1</v>
@@ -2154,7 +2221,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2184,27 +2251,83 @@
         <v>100</v>
       </c>
       <c r="K23" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="10">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="8">
-        <v>-1</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>-1</v>
-      </c>
-      <c r="R23" s="2">
+      <c r="P24" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R24" s="2">
         <v>0</v>
       </c>
     </row>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821EB397-3209-4436-AF4E-B76329AB3D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BB4416-85FB-4B6E-8F6F-95476220E0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="360" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="390" yWindow="570" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -185,9 +185,6 @@
     <t>Ground</t>
   </si>
   <si>
-    <t>Resource/Texture/aerial_grass_rock_nor_dx_4k.png</t>
-  </si>
-  <si>
     <t>Billboard</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Resource/Texture/aerial_grass_rock_diff_4k.png</t>
-  </si>
-  <si>
     <t>Resource/Texture/Billboard.png</t>
   </si>
   <si>
@@ -311,6 +305,18 @@
   </si>
   <si>
     <t>Resource/Texture/Particle/Particle04_bokashi_hard.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/asphalt_02_diff_2k.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/asphalt_02_nor_dx_2k.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/asphalt_02_rough_2k.png</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1045,7 +1051,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2">
         <v>0.4</v>
@@ -1087,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P2" s="8" t="s">
         <v>38</v>
@@ -1143,13 +1149,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -1199,13 +1205,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -1311,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P6" s="8">
         <v>-1</v>
@@ -1423,10 +1429,10 @@
         <v>200</v>
       </c>
       <c r="O8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="Q8" s="8">
         <v>-1</v>
@@ -1538,7 +1544,7 @@
         <v>30</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q10" s="8" t="s">
         <v>31</v>
@@ -1605,7 +1611,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1647,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q12" s="8">
         <v>-1</v>
@@ -1661,7 +1667,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1703,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>38</v>
@@ -1717,7 +1723,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1759,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>38</v>
@@ -1773,7 +1779,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1815,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>38</v>
@@ -1983,13 +1989,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>-1</v>
+        <v>77</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
@@ -1997,7 +2003,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A19" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="15">
         <v>1</v>
@@ -2039,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P19" s="8">
         <v>-1</v>
@@ -2053,7 +2059,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2095,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P20" s="3">
         <v>-1</v>
@@ -2109,7 +2115,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
@@ -2151,10 +2157,10 @@
         <v>0.1</v>
       </c>
       <c r="O21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="Q21" s="8">
         <v>-1</v>
@@ -2165,7 +2171,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2207,10 +2213,10 @@
         <v>1</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q22" s="8">
         <v>-1</v>
@@ -2221,7 +2227,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2263,10 +2269,10 @@
         <v>1.5</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q23" s="8">
         <v>-1</v>
@@ -2277,7 +2283,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -2319,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P24" s="8">
         <v>-1</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BB4416-85FB-4B6E-8F6F-95476220E0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAF5BF5-71C7-4EE6-B681-B9C02B3DE634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="570" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -301,21 +301,54 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Resource/Texture/Particle/Particle04_bokashi_hard.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/asphalt_02_diff_2k.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/asphalt_02_nor_dx_2k.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/asphalt_02_rough_2k.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Recovery_Billboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Item/Recovery.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RecoveryPlus_Billboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Weapon_Billboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>LaserPointBillboard</t>
-  </si>
-  <si>
-    <t>Resource/Texture/Particle/Particle04_bokashi_hard.png</t>
-  </si>
-  <si>
-    <t>Resource/Texture/Materials/asphalt_02_diff_2k.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Materials/asphalt_02_nor_dx_2k.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Materials/asphalt_02_rough_2k.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Armor_Billboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Item/RecoveryPlus.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Item/Armor.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Item/WeaponBox.png</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -982,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1989,13 +2022,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="P18" s="8" t="s">
+      <c r="Q18" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
@@ -2059,7 +2092,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2101,7 +2134,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="P20" s="3">
         <v>-1</v>
@@ -2114,226 +2147,450 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3">
+        <v>50</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>5</v>
+      </c>
+      <c r="O21" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-1</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-1</v>
+      </c>
+      <c r="R21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A22" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
+        <v>50</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>5</v>
+      </c>
+      <c r="O22" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="P22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="R22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A23" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3">
+        <v>50</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>5</v>
+      </c>
+      <c r="O23" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-1</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-1</v>
+      </c>
+      <c r="R23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A24" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3">
+        <v>50</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>5</v>
+      </c>
+      <c r="O24" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-1</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-1</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="2">
-        <v>1</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="9">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="9">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2">
         <v>50</v>
       </c>
-      <c r="K21" s="11">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2">
-        <v>1</v>
-      </c>
-      <c r="N21" s="2">
+      <c r="K25" s="11">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1</v>
+      </c>
+      <c r="M25" s="2">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2">
         <v>0.1</v>
       </c>
-      <c r="O21" s="8" t="s">
+      <c r="O25" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="P21" s="8" t="s">
+      <c r="P25" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="Q21" s="8">
-        <v>-1</v>
-      </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A22" s="3" t="s">
+      <c r="Q25" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="3">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3">
-        <v>1</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1</v>
-      </c>
-      <c r="I22" s="10">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="10">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="12">
-        <v>1</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1</v>
-      </c>
-      <c r="O22" s="8" t="s">
+      <c r="K26" s="12">
+        <v>1</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="P22" s="8" t="s">
+      <c r="P26" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="Q22" s="8">
-        <v>-1</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A23" s="3" t="s">
+      <c r="Q26" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A27" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="3">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1</v>
-      </c>
-      <c r="I23" s="10">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="10">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="12">
-        <v>1</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3">
-        <v>1</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="K27" s="12">
+        <v>1</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3">
+        <v>1</v>
+      </c>
+      <c r="N27" s="3">
         <v>1.5</v>
       </c>
-      <c r="O23" s="8" t="s">
+      <c r="O27" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="P23" s="8" t="s">
+      <c r="P27" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="Q23" s="8">
-        <v>-1</v>
-      </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A24" s="3" t="s">
+      <c r="Q27" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="3">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" s="10">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="10">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="12">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="8" t="s">
+      <c r="K28" s="12">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="P24" s="8">
-        <v>-1</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>-1</v>
-      </c>
-      <c r="R24" s="2">
+      <c r="P28" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R28" s="2">
         <v>0</v>
       </c>
     </row>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAF5BF5-71C7-4EE6-B681-B9C02B3DE634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616B2854-F39A-4393-AE8F-539006D4E316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="570" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="8490" yWindow="585" windowWidth="27345" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="88">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -328,10 +331,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Weapon_Billboard</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>LaserPointBillboard</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -349,6 +348,14 @@
   </si>
   <si>
     <t>Resource/Texture/Item/WeaponBox.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/DefaultN_Map.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WeaponBox_Billboard</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1969,7 +1976,7 @@
         <v>40</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="Q17" s="8">
         <v>-1</v>
@@ -2190,7 +2197,7 @@
         <v>5</v>
       </c>
       <c r="O21" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P21" s="3">
         <v>-1</v>
@@ -2204,7 +2211,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2246,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="O22" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P22" s="3">
         <v>-1</v>
@@ -2260,7 +2267,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2302,7 +2309,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P23" s="3">
         <v>-1</v>
@@ -2316,10 +2323,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2584,8 +2591,8 @@
       <c r="O28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="P28" s="8">
-        <v>-1</v>
+      <c r="P28" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="Q28" s="8">
         <v>-1</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616B2854-F39A-4393-AE8F-539006D4E316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6B4C3A3-582C-4FD3-AB95-E6AFFF343EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8490" yWindow="585" windowWidth="27345" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="3090" yWindow="-14835" windowWidth="19710" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="94">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -224,9 +224,6 @@
     <t>Resource/Texture/BulletHole.png</t>
   </si>
   <si>
-    <t>Resource/Texture/Acid.png</t>
-  </si>
-  <si>
     <t>Resource/Model/b-2/textures/ggg_normal.jpeg</t>
   </si>
   <si>
@@ -356,6 +353,34 @@
   </si>
   <si>
     <t>WeaponBox_Billboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bullet_01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/Acid.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/Particle04_bokashi_hard.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/Ant_Hit1.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bullet_02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bullet_03</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1022,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1189,13 +1214,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -1245,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>64</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -1584,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q10" s="8" t="s">
         <v>31</v>
@@ -1651,7 +1676,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1693,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q12" s="8">
         <v>-1</v>
@@ -1707,7 +1732,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1749,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>38</v>
@@ -1763,7 +1788,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1805,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>38</v>
@@ -1819,7 +1844,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1861,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>38</v>
@@ -1976,7 +2001,7 @@
         <v>40</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q17" s="8">
         <v>-1</v>
@@ -2029,13 +2054,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="P18" s="8" t="s">
+      <c r="Q18" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
@@ -2099,7 +2124,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2141,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P20" s="3">
         <v>-1</v>
@@ -2155,7 +2180,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -2197,7 +2222,7 @@
         <v>5</v>
       </c>
       <c r="O21" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P21" s="3">
         <v>-1</v>
@@ -2211,7 +2236,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2253,7 +2278,7 @@
         <v>5</v>
       </c>
       <c r="O22" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P22" s="3">
         <v>-1</v>
@@ -2267,7 +2292,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2309,7 +2334,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P23" s="3">
         <v>-1</v>
@@ -2323,7 +2348,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="3">
         <v>5</v>
@@ -2365,7 +2390,7 @@
         <v>5</v>
       </c>
       <c r="O24" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P24" s="3">
         <v>-1</v>
@@ -2480,7 +2505,7 @@
         <v>52</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q26" s="8">
         <v>-1</v>
@@ -2533,21 +2558,21 @@
         <v>1.5</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q27" s="8">
         <v>-1</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -2589,16 +2614,240 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q28" s="8">
         <v>-1</v>
       </c>
       <c r="R28" s="2">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3">
+        <v>10</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1</v>
+      </c>
+      <c r="I29" s="10">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3">
+        <v>100</v>
+      </c>
+      <c r="K29" s="12">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P29" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" s="10">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3">
+        <v>100</v>
+      </c>
+      <c r="K30" s="12">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P30" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="3">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="10">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3">
+        <v>100</v>
+      </c>
+      <c r="K31" s="12">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P31" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="10">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="12">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="P32" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6B4C3A3-582C-4FD3-AB95-E6AFFF343EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FE1F3575-9B00-4696-B92B-B8C673032653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="-14835" windowWidth="19710" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="390" yWindow="570" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="96">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -381,6 +378,14 @@
   </si>
   <si>
     <t>Bullet_03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/Flame1.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flame_01</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1047,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -2387,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O24" s="19" t="s">
         <v>73</v>
@@ -2658,16 +2663,16 @@
         <v>100</v>
       </c>
       <c r="K29" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="8" t="s">
         <v>90</v>
@@ -2714,16 +2719,16 @@
         <v>100</v>
       </c>
       <c r="K30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>90</v>
@@ -2770,16 +2775,16 @@
         <v>100</v>
       </c>
       <c r="K31" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="8" t="s">
         <v>90</v>
@@ -2847,6 +2852,62 @@
         <v>-1</v>
       </c>
       <c r="R32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="3">
+        <v>4</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="10">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3">
+        <v>100</v>
+      </c>
+      <c r="K33" s="12">
+        <v>1</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>5</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="P33" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R33" s="3">
         <v>1</v>
       </c>
     </row>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FE1F3575-9B00-4696-B92B-B8C673032653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49835A45-2810-4734-A788-99384B268243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="570" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="3090" yWindow="-14835" windowWidth="19710" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2860,7 +2863,7 @@
         <v>95</v>
       </c>
       <c r="B33" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" s="3">
         <v>1</v>
@@ -2896,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O33" s="8" t="s">
         <v>94</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49835A45-2810-4734-A788-99384B268243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DDDEC1-3FD1-4D3E-8A9D-C31E7808A926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="-14835" windowWidth="19710" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="735" yWindow="915" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="96">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -221,18 +218,9 @@
     <t>Resource/Texture/Billboard.png</t>
   </si>
   <si>
-    <t>Resource/Texture/BulletHole.png</t>
-  </si>
-  <si>
     <t>Resource/Model/b-2/textures/ggg_normal.jpeg</t>
   </si>
   <si>
-    <t>Resource/Texture/BulletHole_n.png</t>
-  </si>
-  <si>
-    <t>Resource/Texture/Acid_n.png</t>
-  </si>
-  <si>
     <t>RocketLauncher</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -360,14 +348,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Acid</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Particle/Acid.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Resource/Texture/Particle/Particle04_bokashi_hard.png</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -389,6 +369,26 @@
   </si>
   <si>
     <t>Flame_01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/Ant_Hit1_n.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/BulletHole.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/BulletHole_n.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Acid_02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Acid_01</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1055,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1222,13 +1222,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -1278,13 +1278,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>30</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q10" s="8" t="s">
         <v>31</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q12" s="8">
         <v>-1</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>38</v>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>38</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>38</v>
@@ -2009,7 +2009,7 @@
         <v>40</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="8">
         <v>-1</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2174,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P20" s="3">
         <v>-1</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         <v>5</v>
       </c>
       <c r="O21" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P21" s="3">
         <v>-1</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="O22" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P22" s="3">
         <v>-1</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2342,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P23" s="3">
         <v>-1</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B24" s="3">
         <v>5</v>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P24" s="3">
         <v>-1</v>
@@ -2510,10 +2510,10 @@
         <v>1</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="Q26" s="8">
         <v>-1</v>
@@ -2566,10 +2566,10 @@
         <v>1.5</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q27" s="8">
         <v>-1</v>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -2622,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q28" s="8">
         <v>-1</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -2678,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P29" s="8">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
@@ -2734,7 +2734,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P30" s="8">
         <v>-1</v>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B31" s="3">
         <v>10</v>
@@ -2790,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P31" s="8">
         <v>-1</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="P32" s="8">
-        <v>-1</v>
       </c>
       <c r="Q32" s="8">
         <v>-1</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="3">
         <v>5</v>
@@ -2890,7 +2890,7 @@
         <v>100</v>
       </c>
       <c r="K33" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -2899,18 +2899,74 @@
         <v>0</v>
       </c>
       <c r="N33" s="3">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="3">
+        <v>5</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="10">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3">
+        <v>100</v>
+      </c>
+      <c r="K34" s="12">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
         <v>10</v>
       </c>
-      <c r="O33" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="P33" s="8">
-        <v>-1</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>-1</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="O34" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="P34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="3">
         <v>1</v>
       </c>
     </row>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DDDEC1-3FD1-4D3E-8A9D-C31E7808A926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42CA2D4-5F4A-4B28-8497-BFE17C3B7E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="915" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -292,18 +292,6 @@
     <t>Resource/Texture/Particle/Particle04_bokashi_hard.png</t>
   </si>
   <si>
-    <t>Resource/Texture/Materials/asphalt_02_diff_2k.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Materials/asphalt_02_nor_dx_2k.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/Materials/asphalt_02_rough_2k.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Recovery_Billboard</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -390,6 +378,12 @@
   <si>
     <t>Acid_01</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/brick_moss_001_diff_2k.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Materials/brick_moss_001_nor_dx_2k.png</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2003,7 @@
         <v>40</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="8">
         <v>-1</v>
@@ -2047,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K18" s="12">
         <v>1</v>
@@ -2062,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>73</v>
+        <v>94</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>-1</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
@@ -2132,7 +2126,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2174,7 +2168,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P20" s="3">
         <v>-1</v>
@@ -2188,7 +2182,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -2230,7 +2224,7 @@
         <v>5</v>
       </c>
       <c r="O21" s="19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P21" s="3">
         <v>-1</v>
@@ -2244,7 +2238,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2286,7 +2280,7 @@
         <v>5</v>
       </c>
       <c r="O22" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P22" s="3">
         <v>-1</v>
@@ -2300,7 +2294,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2342,7 +2336,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P23" s="3">
         <v>-1</v>
@@ -2356,7 +2350,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3">
         <v>5</v>
@@ -2450,8 +2444,8 @@
       <c r="M25" s="2">
         <v>1</v>
       </c>
-      <c r="N25" s="2">
-        <v>0.1</v>
+      <c r="N25" s="3">
+        <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
         <v>45</v>
@@ -2510,10 +2504,10 @@
         <v>1</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="8">
         <v>-1</v>
@@ -2566,10 +2560,10 @@
         <v>1.5</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q27" s="8">
         <v>-1</v>
@@ -2625,7 +2619,7 @@
         <v>54</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q28" s="8">
         <v>-1</v>
@@ -2636,7 +2630,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -2678,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P29" s="8">
         <v>-1</v>
@@ -2692,7 +2686,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
@@ -2734,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P30" s="8">
         <v>-1</v>
@@ -2748,7 +2742,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B31" s="3">
         <v>10</v>
@@ -2790,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P31" s="8">
         <v>-1</v>
@@ -2804,7 +2798,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
@@ -2846,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q32" s="8">
         <v>-1</v>
@@ -2860,7 +2854,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B33" s="3">
         <v>5</v>
@@ -2902,10 +2896,10 @@
         <v>1</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q33" s="8">
         <v>-1</v>
@@ -2916,7 +2910,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B34" s="3">
         <v>5</v>
@@ -2958,7 +2952,7 @@
         <v>10</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P34" s="8">
         <v>-1</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42CA2D4-5F4A-4B28-8497-BFE17C3B7E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07254415-EBAC-4030-B92C-F9135B7F99A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="915" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="1200" yWindow="-14010" windowWidth="19710" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2913,7 +2916,7 @@
         <v>87</v>
       </c>
       <c r="B34" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -2940,7 +2943,7 @@
         <v>100</v>
       </c>
       <c r="K34" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L34" s="3">
         <v>0</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07254415-EBAC-4030-B92C-F9135B7F99A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68EA9830-2979-4A0F-9BD9-9C527AEA51F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="-14010" windowWidth="19710" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="735" yWindow="915" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2804,13 +2801,13 @@
         <v>92</v>
       </c>
       <c r="B32" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>1</v>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68EA9830-2979-4A0F-9BD9-9C527AEA51F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8A7D5C-479F-42C5-A52A-C899B3A9616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="915" windowWidth="27630" windowHeight="12765" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="6120" yWindow="30" windowWidth="21570" windowHeight="14730" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -136,12 +139,6 @@
     <t>Canonn</t>
   </si>
   <si>
-    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant.png</t>
-  </si>
-  <si>
-    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant_n.png</t>
-  </si>
-  <si>
     <t>Ant</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -384,6 +381,26 @@
   </si>
   <si>
     <t>Resource/Texture/Materials/brick_moss_001_nor_dx_2k.png</t>
+  </si>
+  <si>
+    <t>Objector_body</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Objector_shield</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Enemy/GiantAnt01/textures/new_bake_ant.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Enemy/GiantAnt01/textures/new_bake_ant_n.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Enemy/Octahedron/textures/shieldSurface.jpg</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1049,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1118,7 +1135,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2">
         <v>0.4</v>
@@ -1160,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="8">
         <v>-1</v>
@@ -1216,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -1272,13 +1289,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -1384,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P6" s="8">
         <v>-1</v>
@@ -1496,10 +1513,10 @@
         <v>200</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="8">
         <v>-1</v>
@@ -1510,7 +1527,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -1525,13 +1542,13 @@
         <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
@@ -1552,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="Q9" s="8">
         <v>-1</v>
@@ -1566,7 +1583,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -1608,13 +1625,13 @@
         <v>0</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R10" s="2">
         <v>0</v>
@@ -1622,7 +1639,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -1664,13 +1681,13 @@
         <v>0</v>
       </c>
       <c r="O11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="P11" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="Q11" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
@@ -1678,7 +1695,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -1720,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q12" s="8">
         <v>-1</v>
@@ -1734,7 +1751,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1776,10 +1793,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q13" s="8">
         <v>-1</v>
@@ -1790,7 +1807,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1832,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="8">
         <v>-1</v>
@@ -1846,7 +1863,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1888,10 +1905,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q15" s="8">
         <v>-1</v>
@@ -1902,7 +1919,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -1944,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="8">
         <v>-1</v>
@@ -1958,7 +1975,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
@@ -2000,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="8">
         <v>-1</v>
@@ -2014,7 +2031,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -2056,10 +2073,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q18" s="8">
         <v>-1</v>
@@ -2070,7 +2087,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A19" s="15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" s="15">
         <v>1</v>
@@ -2112,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P19" s="8">
         <v>-1</v>
@@ -2126,7 +2143,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -2168,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P20" s="3">
         <v>-1</v>
@@ -2182,7 +2199,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -2224,7 +2241,7 @@
         <v>5</v>
       </c>
       <c r="O21" s="19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P21" s="3">
         <v>-1</v>
@@ -2238,7 +2255,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -2280,7 +2297,7 @@
         <v>5</v>
       </c>
       <c r="O22" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P22" s="3">
         <v>-1</v>
@@ -2294,7 +2311,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -2336,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P23" s="3">
         <v>-1</v>
@@ -2350,7 +2367,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3">
         <v>5</v>
@@ -2392,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P24" s="3">
         <v>-1</v>
@@ -2406,7 +2423,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2">
         <v>1</v>
@@ -2448,10 +2465,10 @@
         <v>0</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q25" s="8">
         <v>-1</v>
@@ -2462,7 +2479,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B26" s="3">
         <v>1</v>
@@ -2504,10 +2521,10 @@
         <v>1</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q26" s="8">
         <v>-1</v>
@@ -2518,7 +2535,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B27" s="3">
         <v>1</v>
@@ -2560,10 +2577,10 @@
         <v>1.5</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q27" s="8">
         <v>-1</v>
@@ -2574,7 +2591,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -2616,10 +2633,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q28" s="8">
         <v>-1</v>
@@ -2630,7 +2647,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -2672,7 +2689,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P29" s="8">
         <v>-1</v>
@@ -2686,7 +2703,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
@@ -2728,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P30" s="8">
         <v>-1</v>
@@ -2742,7 +2759,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B31" s="3">
         <v>10</v>
@@ -2784,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P31" s="8">
         <v>-1</v>
@@ -2798,7 +2815,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B32" s="3">
         <v>2</v>
@@ -2840,10 +2857,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q32" s="8">
         <v>-1</v>
@@ -2854,7 +2871,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B33" s="3">
         <v>5</v>
@@ -2896,10 +2913,10 @@
         <v>1</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q33" s="8">
         <v>-1</v>
@@ -2910,7 +2927,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B34" s="3">
         <v>10</v>
@@ -2952,7 +2969,7 @@
         <v>10</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P34" s="8">
         <v>-1</v>
@@ -2961,6 +2978,118 @@
         <v>-1</v>
       </c>
       <c r="R34" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="10">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3">
+        <v>100</v>
+      </c>
+      <c r="K35" s="12">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>1</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>3</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P35" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R35" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A36" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3">
+        <v>1</v>
+      </c>
+      <c r="I36" s="10">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
+        <v>100</v>
+      </c>
+      <c r="K36" s="12">
+        <v>0</v>
+      </c>
+      <c r="L36" s="12">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12">
+        <v>0</v>
+      </c>
+      <c r="N36" s="12">
+        <v>0</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P36" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R36" s="3">
         <v>1</v>
       </c>
     </row>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_GraphicFramework\DX11MyEngine\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8A7D5C-479F-42C5-A52A-C899B3A9616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DF004D-F61B-48F5-963B-0FFDF151AEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="30" windowWidth="21570" windowHeight="14730" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialParam" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -400,6 +397,22 @@
   </si>
   <si>
     <t>Resource/Model/Enemy/Octahedron/textures/shieldSurface.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MuzzleFlash_1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MuzzleFlash_2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/MazzleFrash1.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Particle/MazzleFrash2.png</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1066,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -3093,6 +3106,118 @@
         <v>1</v>
       </c>
     </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A37" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <v>1</v>
+      </c>
+      <c r="I37" s="10">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3">
+        <v>100</v>
+      </c>
+      <c r="K37" s="12">
+        <v>0</v>
+      </c>
+      <c r="L37" s="12">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12">
+        <v>0</v>
+      </c>
+      <c r="N37" s="12">
+        <v>0</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="P37" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R37" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="10">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3">
+        <v>100</v>
+      </c>
+      <c r="K38" s="12">
+        <v>0</v>
+      </c>
+      <c r="L38" s="12">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12">
+        <v>0</v>
+      </c>
+      <c r="N38" s="12">
+        <v>0</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="P38" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>-1</v>
+      </c>
+      <c r="R38" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
+++ b/DX11MyEngine/Resource/Excel_Param/MaterialParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\DX11MyEngine\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DF004D-F61B-48F5-963B-0FFDF151AEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F92C22-FCD6-402A-AD64-63D38D8FCCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
